--- a/docs/Test_Report/Cdd_Pwm/TestPlanExecutionReport_Cdd_Pwm.xlsx
+++ b/docs/Test_Report/Cdd_Pwm/TestPlanExecutionReport_Cdd_Pwm.xlsx
@@ -716,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756,MCAL-30822</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10 02:40:41.752702-05:00 CDT</t>
+          <t>2025-06-09 07:29:10.975732-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1561,7 +1561,39 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -1581,7 +1613,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -1596,12 +1628,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1615,12 +1647,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1652,7 +1684,39 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test9",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test9/Cdd_Pwm_Test9.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1672,7 +1736,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1687,12 +1751,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1706,12 +1770,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1743,7 +1807,39 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test6",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test6/Cdd_Pwm_Test6.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1763,7 +1859,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1778,12 +1874,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1797,12 +1893,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1834,7 +1930,39 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test5",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test5/Cdd_Pwm_Test5.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1854,7 +1982,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1869,12 +1997,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -1888,12 +2016,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1925,7 +2053,39 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test7",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test7/Cdd_Pwm_Test7.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1945,7 +2105,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1960,12 +2120,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -1979,12 +2139,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2016,7 +2176,39 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test4",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test4/Cdd_Pwm_Test4.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2036,7 +2228,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -2051,12 +2243,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2070,12 +2262,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2107,7 +2299,39 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test3",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test3/Cdd_Pwm_Test3.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2127,7 +2351,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2142,12 +2366,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2161,12 +2385,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2198,7 +2422,39 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test8",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test8/Cdd_Pwm_Test8.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -2218,7 +2474,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2233,12 +2489,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2252,12 +2508,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2289,7 +2545,39 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -2309,7 +2597,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2324,12 +2612,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2343,12 +2631,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2380,7 +2668,39 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test2/Cdd_Pwm_Test2.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -2400,7 +2720,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2415,12 +2735,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2434,12 +2754,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2471,7 +2791,39 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -2491,7 +2843,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2506,12 +2858,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2525,12 +2877,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2562,7 +2914,39 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -2582,7 +2966,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2597,12 +2981,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -2616,12 +3000,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2653,7 +3037,39 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2673,7 +3089,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2688,12 +3104,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -2707,12 +3123,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2744,7 +3160,39 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2764,7 +3212,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2779,12 +3227,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -2798,12 +3246,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2835,7 +3283,39 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2855,7 +3335,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2870,12 +3350,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -2889,12 +3369,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2926,7 +3406,39 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -2946,7 +3458,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2961,12 +3473,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -2980,12 +3492,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3017,7 +3529,39 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -3037,7 +3581,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -3052,12 +3596,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3071,12 +3615,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3108,7 +3652,39 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -3128,7 +3704,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3143,12 +3719,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3162,12 +3738,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -3199,7 +3775,39 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -3219,7 +3827,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3234,12 +3842,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -3253,12 +3861,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -3290,7 +3898,39 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -3310,7 +3950,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3325,12 +3965,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -3344,12 +3984,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3381,7 +4021,39 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -3401,7 +4073,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3416,12 +4088,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -3435,12 +4107,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3472,7 +4144,39 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3492,7 +4196,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3507,12 +4211,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -3526,12 +4230,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3563,7 +4267,39 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -3583,7 +4319,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3598,12 +4334,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -3617,12 +4353,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3654,7 +4390,39 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3675,7 +4443,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3690,12 +4458,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -3709,12 +4477,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3746,7 +4514,39 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -3767,7 +4567,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3782,12 +4582,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -3801,12 +4601,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3838,7 +4638,39 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -3858,7 +4690,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3873,12 +4705,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -3892,12 +4724,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3929,7 +4761,39 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -3949,7 +4813,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3964,12 +4828,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -3983,12 +4847,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4020,7 +4884,39 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -4040,7 +4936,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4055,12 +4951,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -4074,12 +4970,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4111,7 +5007,39 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4131,7 +5059,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4146,12 +5074,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -4165,12 +5093,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -4202,7 +5130,39 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -4222,7 +5182,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4237,12 +5197,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -4256,12 +5216,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -4293,7 +5253,39 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4313,7 +5305,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4328,12 +5320,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -4347,12 +5339,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4384,7 +5376,39 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -4404,7 +5428,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4419,12 +5443,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -4438,12 +5462,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4475,7 +5499,39 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -4495,7 +5551,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4510,12 +5566,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -4529,12 +5585,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4566,7 +5622,39 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -4586,7 +5674,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4601,12 +5689,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -4620,12 +5708,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4657,7 +5745,39 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -4677,7 +5797,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -4692,12 +5812,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -4711,12 +5831,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -4748,7 +5868,39 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -4768,7 +5920,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -4783,12 +5935,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -4802,12 +5954,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4839,7 +5991,39 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -4859,7 +6043,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -4874,12 +6058,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -4893,12 +6077,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -4930,7 +6114,39 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -4950,7 +6166,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -4965,12 +6181,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -4984,12 +6200,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -5021,7 +6237,39 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -5041,7 +6289,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5056,12 +6304,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -5075,12 +6323,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5112,7 +6360,39 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -5132,7 +6412,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5147,12 +6427,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -5166,12 +6446,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5203,7 +6483,39 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -5223,7 +6535,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5238,12 +6550,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -5257,12 +6569,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5294,7 +6606,39 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -5314,7 +6658,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5329,12 +6673,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -5348,12 +6692,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5385,7 +6729,39 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -5405,7 +6781,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -5420,12 +6796,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -5439,12 +6815,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5476,7 +6852,39 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -5496,7 +6904,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -5511,12 +6919,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -5530,12 +6938,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5567,7 +6975,39 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -5587,7 +7027,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -5602,12 +7042,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -5621,12 +7061,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -5658,7 +7098,39 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -5678,7 +7150,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -5693,12 +7165,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -5712,12 +7184,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5749,7 +7221,39 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -5769,7 +7273,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -5784,12 +7288,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -5803,12 +7307,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -5840,7 +7344,39 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -5860,7 +7396,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -5875,12 +7411,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -5894,12 +7430,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5931,7 +7467,39 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -5951,7 +7519,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -5966,12 +7534,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -5985,12 +7553,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -6022,7 +7590,39 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
@@ -6042,7 +7642,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -6057,12 +7657,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -6076,12 +7676,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -6113,7 +7713,39 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -6133,7 +7765,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -6148,12 +7780,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -6167,12 +7799,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -6204,7 +7836,39 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -6224,7 +7888,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -6239,12 +7903,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -6258,12 +7922,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -6295,7 +7959,39 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
@@ -6315,7 +8011,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -6330,12 +8026,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -6349,12 +8045,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -6386,7 +8082,39 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -6406,7 +8134,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -6421,12 +8149,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -6440,12 +8168,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -6477,7 +8205,39 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -6497,7 +8257,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -6512,12 +8272,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -6531,12 +8291,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -6568,7 +8328,39 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -6588,7 +8380,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -6603,12 +8395,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -6622,12 +8414,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6659,7 +8451,39 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -6679,7 +8503,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -6694,12 +8518,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -6713,12 +8537,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6750,7 +8574,39 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
@@ -6770,7 +8626,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -6785,12 +8641,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -6804,12 +8660,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -6841,7 +8697,39 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -6861,7 +8749,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -6876,12 +8764,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -6895,12 +8783,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30762</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -6932,7 +8820,39 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Cdd_Pwm_Test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Cdd_Pwm_Test1/Cdd_Pwm_Test1.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
@@ -6952,7 +8872,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
@@ -6967,12 +8887,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30756</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Automated Test Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -6986,12 +8906,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30259</t>
+          <t>MCAL-30821</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Manual Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -7058,12 +8978,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30258</t>
+          <t>MCAL-30822</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00: CDD PWM - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01: CDD PWM - Manual Test Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
